--- a/exports/trend_1d/ABB_full_report.xlsx
+++ b/exports/trend_1d/ABB_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42073</v>
+        <v>42074</v>
       </c>
       <c r="H2" t="n">
-        <v>1038.7</v>
+        <v>1026.8</v>
       </c>
       <c r="I2" t="n">
         <v>1032.075184986992</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K2" t="n">
-        <v>4.76</v>
+        <v>3.56</v>
       </c>
       <c r="L2" t="n">
         <v>1.81</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>12.47</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42095</v>
+        <v>42100</v>
       </c>
       <c r="H3" t="n">
-        <v>998.85</v>
+        <v>1051</v>
       </c>
       <c r="I3" t="n">
         <v>1043.101350263773</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K3" t="n">
-        <v>2.72</v>
+        <v>-2.36</v>
       </c>
       <c r="L3" t="n">
-        <v>4.4</v>
+        <v>5.08</v>
       </c>
       <c r="M3" t="n">
         <v>0.92</v>
       </c>
       <c r="N3" t="n">
-        <v>3.66</v>
+        <v>5.22</v>
       </c>
       <c r="O3" t="n">
         <v>-1.15</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>11.76</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42157</v>
+        <v>42158</v>
       </c>
       <c r="H4" t="n">
-        <v>1029.5</v>
+        <v>990.55</v>
       </c>
       <c r="I4" t="n">
         <v>994.120083003743</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.05</v>
+        <v>-5.75</v>
       </c>
       <c r="L4" t="n">
-        <v>5.09</v>
+        <v>6.26</v>
       </c>
       <c r="M4" t="n">
         <v>3.76</v>
       </c>
       <c r="N4" t="n">
-        <v>2.47</v>
+        <v>3.78</v>
       </c>
       <c r="O4" t="n">
         <v>5.22</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>11.31</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42187</v>
+        <v>42188</v>
       </c>
       <c r="H5" t="n">
-        <v>1064.4</v>
+        <v>1091.1</v>
       </c>
       <c r="I5" t="n">
         <v>1073.521771317506</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.46</v>
+        <v>-10.15</v>
       </c>
       <c r="L5" t="n">
-        <v>8.85</v>
+        <v>10.55</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="N5" t="n">
         <v>4.29</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>9.73</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42228</v>
+        <v>42229</v>
       </c>
       <c r="H6" t="n">
-        <v>1038.2</v>
+        <v>1005.6</v>
       </c>
       <c r="I6" t="n">
         <v>1020.89866563145</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.85</v>
+        <v>-7.84</v>
       </c>
       <c r="L6" t="n">
-        <v>6.19</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.09</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42292</v>
+        <v>42293</v>
       </c>
       <c r="H7" t="n">
-        <v>882.9</v>
+        <v>915.05</v>
       </c>
       <c r="I7" t="n">
         <v>896.4008494316981</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K7" t="n">
-        <v>12.2</v>
+        <v>9</v>
       </c>
       <c r="L7" t="n">
         <v>4.89</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.85</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42332</v>
+        <v>42334</v>
       </c>
       <c r="H8" t="n">
-        <v>907.05</v>
+        <v>900.35</v>
       </c>
       <c r="I8" t="n">
         <v>901.8223874642599</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.87</v>
+        <v>-1.61</v>
       </c>
       <c r="L8" t="n">
         <v>3.44</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.4</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42403</v>
+        <v>42404</v>
       </c>
       <c r="H9" t="n">
-        <v>786.5</v>
+        <v>900.4</v>
       </c>
       <c r="I9" t="n">
         <v>827.7821995762724</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K9" t="n">
-        <v>12.65</v>
+        <v>-0.01</v>
       </c>
       <c r="L9" t="n">
         <v>7.1</v>
@@ -954,7 +1061,7 @@
         <v>1.22</v>
       </c>
       <c r="N9" t="n">
-        <v>7.15</v>
+        <v>14.48</v>
       </c>
       <c r="O9" t="n">
         <v>-0.74</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>16.75</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42493</v>
+        <v>42494</v>
       </c>
       <c r="H10" t="n">
-        <v>969.55</v>
+        <v>958.15</v>
       </c>
       <c r="I10" t="n">
         <v>963.370028439331</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K10" t="n">
-        <v>7.68</v>
+        <v>6.41</v>
       </c>
       <c r="L10" t="n">
         <v>13.07</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>11.9</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42569</v>
+        <v>42570</v>
       </c>
       <c r="H11" t="n">
-        <v>994.4</v>
+        <v>1012.45</v>
       </c>
       <c r="I11" t="n">
         <v>1005.121250649725</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.78</v>
+        <v>-5.67</v>
       </c>
       <c r="L11" t="n">
         <v>7.72</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>7.63</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42584</v>
+        <v>42585</v>
       </c>
       <c r="H12" t="n">
-        <v>964.7</v>
+        <v>938.45</v>
       </c>
       <c r="I12" t="n">
         <v>945.8183603006877</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.72</v>
+        <v>-7.31</v>
       </c>
       <c r="L12" t="n">
-        <v>5.39</v>
+        <v>7.79</v>
       </c>
       <c r="M12" t="n">
         <v>0.18</v>
       </c>
       <c r="N12" t="n">
-        <v>2.12</v>
+        <v>2.72</v>
       </c>
       <c r="O12" t="n">
         <v>1.82</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>10.29</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42744</v>
+        <v>42745</v>
       </c>
       <c r="H13" t="n">
-        <v>810.65</v>
+        <v>919.1</v>
       </c>
       <c r="I13" t="n">
         <v>850.7578323796703</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K13" t="n">
-        <v>13.62</v>
+        <v>2.06</v>
       </c>
       <c r="L13" t="n">
         <v>3.73</v>
@@ -1182,7 +1337,7 @@
         <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.44</v>
+        <v>13.38</v>
       </c>
       <c r="O13" t="n">
         <v>-2.72</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>14.13</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42951</v>
+        <v>42954</v>
       </c>
       <c r="H14" t="n">
-        <v>1115.15</v>
+        <v>1099.25</v>
       </c>
       <c r="I14" t="n">
         <v>1101.981564740909</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K14" t="n">
-        <v>21.33</v>
+        <v>19.6</v>
       </c>
       <c r="L14" t="n">
         <v>12.45</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.27</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42991</v>
+        <v>42992</v>
       </c>
       <c r="H15" t="n">
-        <v>1081.35</v>
+        <v>1115.2</v>
       </c>
       <c r="I15" t="n">
         <v>1112.254392860879</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K15" t="n">
-        <v>1.63</v>
+        <v>-1.45</v>
       </c>
       <c r="L15" t="n">
         <v>2.43</v>
@@ -1296,7 +1475,7 @@
         <v>1.28</v>
       </c>
       <c r="N15" t="n">
-        <v>2.41</v>
+        <v>3.13</v>
       </c>
       <c r="O15" t="n">
         <v>-1.43</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>9.51</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43017</v>
+        <v>43018</v>
       </c>
       <c r="H16" t="n">
-        <v>1075.4</v>
+        <v>1058.35</v>
       </c>
       <c r="I16" t="n">
         <v>1060.380558510886</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.57</v>
+        <v>-5.1</v>
       </c>
       <c r="L16" t="n">
-        <v>4.37</v>
+        <v>5.31</v>
       </c>
       <c r="M16" t="n">
         <v>0.09</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>10.05</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43111</v>
+        <v>43112</v>
       </c>
       <c r="H17" t="n">
-        <v>1094.35</v>
+        <v>1155.5</v>
       </c>
       <c r="I17" t="n">
         <v>1128.974873270801</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.4</v>
+        <v>-9.18</v>
       </c>
       <c r="L17" t="n">
-        <v>7.71</v>
+        <v>12.22</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>2.32</v>
+        <v>5.59</v>
       </c>
       <c r="O17" t="n">
         <v>-1.59</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.23</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43147</v>
+        <v>43150</v>
       </c>
       <c r="H18" t="n">
-        <v>1184.3</v>
+        <v>1162.95</v>
       </c>
       <c r="I18" t="n">
         <v>1172.796403545654</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K18" t="n">
-        <v>2.49</v>
+        <v>0.64</v>
       </c>
       <c r="L18" t="n">
         <v>5.05</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>12.83</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43213</v>
+        <v>43214</v>
       </c>
       <c r="H19" t="n">
-        <v>1042.5</v>
+        <v>1058.4</v>
       </c>
       <c r="I19" t="n">
         <v>1044.208448302267</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K19" t="n">
-        <v>10.36</v>
+        <v>8.99</v>
       </c>
       <c r="L19" t="n">
         <v>4.21</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>7.49</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43230</v>
+        <v>43231</v>
       </c>
       <c r="H20" t="n">
-        <v>991.55</v>
+        <v>973.6</v>
       </c>
       <c r="I20" t="n">
         <v>979.1148411876469</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.32</v>
+        <v>-8.01</v>
       </c>
       <c r="L20" t="n">
-        <v>7.51</v>
+        <v>8.74</v>
       </c>
       <c r="M20" t="n">
         <v>0.58</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>9.81</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43262</v>
+        <v>43263</v>
       </c>
       <c r="H21" t="n">
-        <v>976.85</v>
+        <v>1004.2</v>
       </c>
       <c r="I21" t="n">
         <v>988.0030439826437</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.33</v>
+        <v>-3.14</v>
       </c>
       <c r="L21" t="n">
-        <v>2.8</v>
+        <v>3.92</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>11.3</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43300</v>
+        <v>43301</v>
       </c>
       <c r="H22" t="n">
-        <v>905.15</v>
+        <v>887.4</v>
       </c>
       <c r="I22" t="n">
         <v>895.8398886289945</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K22" t="n">
-        <v>-9.859999999999999</v>
+        <v>-11.63</v>
       </c>
       <c r="L22" t="n">
-        <v>10.38</v>
+        <v>12.09</v>
       </c>
       <c r="M22" t="n">
         <v>2.02</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>11.38</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43332</v>
+        <v>43333</v>
       </c>
       <c r="H23" t="n">
-        <v>961.05</v>
+        <v>993.15</v>
       </c>
       <c r="I23" t="n">
         <v>975.019285236419</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.300000000000001</v>
+        <v>-11.92</v>
       </c>
       <c r="L23" t="n">
-        <v>11.84</v>
+        <v>12.96</v>
       </c>
       <c r="M23" t="n">
         <v>2.51</v>
       </c>
       <c r="N23" t="n">
-        <v>2.36</v>
+        <v>3.34</v>
       </c>
       <c r="O23" t="n">
         <v>-1.96</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43383</v>
+        <v>43384</v>
       </c>
       <c r="H24" t="n">
-        <v>1048.85</v>
+        <v>1008.65</v>
       </c>
       <c r="I24" t="n">
         <v>1015.605713911227</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K24" t="n">
-        <v>5.61</v>
+        <v>1.56</v>
       </c>
       <c r="L24" t="n">
         <v>3.23</v>
       </c>
       <c r="M24" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="N24" t="n">
-        <v>3.05</v>
+        <v>3.83</v>
       </c>
       <c r="O24" t="n">
         <v>3.34</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>15.25</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43431</v>
+        <v>43432</v>
       </c>
       <c r="H25" t="n">
-        <v>1060.25</v>
+        <v>1093.95</v>
       </c>
       <c r="I25" t="n">
         <v>1064.008849718872</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.12</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>6.67</v>
+        <v>8.91</v>
       </c>
       <c r="M25" t="n">
         <v>3.26</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.58</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43453</v>
+        <v>43454</v>
       </c>
       <c r="H26" t="n">
-        <v>1043.15</v>
+        <v>1027.55</v>
       </c>
       <c r="I26" t="n">
         <v>1040.424225170695</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.64</v>
+        <v>-6.07</v>
       </c>
       <c r="L26" t="n">
         <v>8.51</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>11.66</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43542</v>
+        <v>43543</v>
       </c>
       <c r="H27" t="n">
-        <v>1020.95</v>
+        <v>1031.8</v>
       </c>
       <c r="I27" t="n">
         <v>1025.007428516865</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K27" t="n">
-        <v>0.64</v>
+        <v>-0.41</v>
       </c>
       <c r="L27" t="n">
         <v>3.33</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>7.55</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43593</v>
+        <v>43594</v>
       </c>
       <c r="H28" t="n">
-        <v>1136.55</v>
+        <v>1083.65</v>
       </c>
       <c r="I28" t="n">
         <v>1084.345816864988</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K28" t="n">
-        <v>10.15</v>
+        <v>5.03</v>
       </c>
       <c r="L28" t="n">
         <v>1.41</v>
@@ -2037,7 +2372,7 @@
         <v>1.17</v>
       </c>
       <c r="N28" t="n">
-        <v>1.9</v>
+        <v>4.65</v>
       </c>
       <c r="O28" t="n">
         <v>1.06</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>10.89</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43608</v>
+        <v>43609</v>
       </c>
       <c r="H29" t="n">
-        <v>1124.15</v>
+        <v>1170.45</v>
       </c>
       <c r="I29" t="n">
         <v>1160.778238690508</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.74</v>
+        <v>-8.01</v>
       </c>
       <c r="L29" t="n">
-        <v>7.51</v>
+        <v>8.23</v>
       </c>
       <c r="M29" t="n">
         <v>2.26</v>
       </c>
       <c r="N29" t="n">
-        <v>3.31</v>
+        <v>4.12</v>
       </c>
       <c r="O29" t="n">
         <v>-4.65</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.76</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H30" t="n">
-        <v>1205.65</v>
+        <v>1158.95</v>
       </c>
       <c r="I30" t="n">
         <v>1183.790257379785</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K30" t="n">
-        <v>3.01</v>
+        <v>-0.98</v>
       </c>
       <c r="L30" t="n">
         <v>3.48</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>13.99</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43728</v>
+        <v>43731</v>
       </c>
       <c r="H31" t="n">
-        <v>1101.8</v>
+        <v>1214.5</v>
       </c>
       <c r="I31" t="n">
         <v>1106.191980402519</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K31" t="n">
-        <v>4.93</v>
+        <v>-4.79</v>
       </c>
       <c r="L31" t="n">
-        <v>6.26</v>
+        <v>8.01</v>
       </c>
       <c r="M31" t="n">
         <v>1.52</v>
       </c>
       <c r="N31" t="n">
-        <v>6.32</v>
+        <v>10.23</v>
       </c>
       <c r="O31" t="n">
         <v>-3.87</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>14.9</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43874</v>
+        <v>43875</v>
       </c>
       <c r="H32" t="n">
-        <v>1268.65</v>
+        <v>1233.1</v>
       </c>
       <c r="I32" t="n">
         <v>1257.2047812305</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K32" t="n">
-        <v>4.46</v>
+        <v>1.53</v>
       </c>
       <c r="L32" t="n">
         <v>9.67</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>13.01</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H33" t="n">
-        <v>821.4</v>
+        <v>824.9</v>
       </c>
       <c r="I33" t="n">
         <v>822.3809520476397</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K33" t="n">
-        <v>33.39</v>
+        <v>33.1</v>
       </c>
       <c r="L33" t="n">
         <v>3.8</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>11.8</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43998</v>
+        <v>43999</v>
       </c>
       <c r="H34" t="n">
-        <v>794.95</v>
+        <v>784.65</v>
       </c>
       <c r="I34" t="n">
         <v>788.7093309854088</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.63</v>
+        <v>-4.88</v>
       </c>
       <c r="L34" t="n">
         <v>5.44</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>13.19</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44007</v>
+        <v>44008</v>
       </c>
       <c r="H35" t="n">
-        <v>880.5</v>
+        <v>914.35</v>
       </c>
       <c r="I35" t="n">
         <v>884.3155809854945</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K35" t="n">
-        <v>-12.22</v>
+        <v>-16.53</v>
       </c>
       <c r="L35" t="n">
-        <v>14.19</v>
+        <v>18.14</v>
       </c>
       <c r="M35" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="N35" t="n">
-        <v>3.24</v>
+        <v>3.84</v>
       </c>
       <c r="O35" t="n">
         <v>-1.3</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>11.24</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44040</v>
+        <v>44041</v>
       </c>
       <c r="H36" t="n">
-        <v>894.5</v>
+        <v>880.95</v>
       </c>
       <c r="I36" t="n">
         <v>887.0707659898983</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.17</v>
+        <v>-3.65</v>
       </c>
       <c r="L36" t="n">
-        <v>3.14</v>
+        <v>4.3</v>
       </c>
       <c r="M36" t="n">
         <v>2.65</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44061</v>
+        <v>44062</v>
       </c>
       <c r="H37" t="n">
-        <v>933.1</v>
+        <v>961.85</v>
       </c>
       <c r="I37" t="n">
         <v>957.1100863834381</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.92</v>
+        <v>-9.18</v>
       </c>
       <c r="L37" t="n">
-        <v>8.970000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="M37" t="n">
         <v>1.35</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>9.59</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44081</v>
+        <v>44082</v>
       </c>
       <c r="H38" t="n">
-        <v>925.05</v>
+        <v>901.15</v>
       </c>
       <c r="I38" t="n">
         <v>906.1414301480031</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.83</v>
+        <v>-6.31</v>
       </c>
       <c r="L38" t="n">
-        <v>4.29</v>
+        <v>6.43</v>
       </c>
       <c r="M38" t="n">
         <v>2.15</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>13.08</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44125</v>
+        <v>44126</v>
       </c>
       <c r="H39" t="n">
-        <v>901.65</v>
+        <v>917.2</v>
       </c>
       <c r="I39" t="n">
         <v>916.3597265623447</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.06</v>
+        <v>-1.78</v>
       </c>
       <c r="L39" t="n">
         <v>4.72</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.73</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44274</v>
+        <v>44277</v>
       </c>
       <c r="H40" t="n">
-        <v>1413.85</v>
+        <v>1388.6</v>
       </c>
       <c r="I40" t="n">
         <v>1397.296727277688</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K40" t="n">
-        <v>54.15</v>
+        <v>51.4</v>
       </c>
       <c r="L40" t="n">
         <v>5.3</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>12.65</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44337</v>
+        <v>44340</v>
       </c>
       <c r="H41" t="n">
-        <v>1433.1</v>
+        <v>1475.7</v>
       </c>
       <c r="I41" t="n">
         <v>1460.060621076311</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.2</v>
+        <v>-6.27</v>
       </c>
       <c r="L41" t="n">
         <v>7.9</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.42</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44411</v>
+        <v>44412</v>
       </c>
       <c r="H42" t="n">
-        <v>1670.7</v>
+        <v>1636.45</v>
       </c>
       <c r="I42" t="n">
         <v>1650.313116823739</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K42" t="n">
-        <v>13.21</v>
+        <v>10.89</v>
       </c>
       <c r="L42" t="n">
         <v>2.89</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>11.24</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44434</v>
+        <v>44435</v>
       </c>
       <c r="H43" t="n">
-        <v>1736.35</v>
+        <v>1850.05</v>
       </c>
       <c r="I43" t="n">
         <v>1793.236345564803</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.1</v>
+        <v>-13.05</v>
       </c>
       <c r="L43" t="n">
-        <v>10.43</v>
+        <v>13.97</v>
       </c>
       <c r="M43" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="N43" t="n">
-        <v>2.62</v>
+        <v>6.55</v>
       </c>
       <c r="O43" t="n">
         <v>-2.05</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>14.16</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44603</v>
+        <v>44606</v>
       </c>
       <c r="H44" t="n">
-        <v>2179.25</v>
+        <v>2091</v>
       </c>
       <c r="I44" t="n">
         <v>2168.163138516368</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K44" t="n">
-        <v>17.79</v>
+        <v>13.02</v>
       </c>
       <c r="L44" t="n">
         <v>6.22</v>
       </c>
       <c r="M44" t="n">
-        <v>2.01</v>
+        <v>3.87</v>
       </c>
       <c r="N44" t="n">
         <v>7.32</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>6</v>
+      </c>
+      <c r="U44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>13.99</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44655</v>
+        <v>44656</v>
       </c>
       <c r="H45" t="n">
-        <v>2130.55</v>
+        <v>2207.55</v>
       </c>
       <c r="I45" t="n">
         <v>2198.934008753681</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.89</v>
+        <v>-5.57</v>
       </c>
       <c r="L45" t="n">
-        <v>7.08</v>
+        <v>8.32</v>
       </c>
       <c r="M45" t="n">
         <v>1.13</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>11.24</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H46" t="n">
-        <v>3124.65</v>
+        <v>3002.2</v>
       </c>
       <c r="I46" t="n">
         <v>3099.823879332771</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K46" t="n">
-        <v>41.54</v>
+        <v>36</v>
       </c>
       <c r="L46" t="n">
         <v>9.4</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>12</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44936</v>
+        <v>44937</v>
       </c>
       <c r="H47" t="n">
-        <v>2841.65</v>
+        <v>2900.2</v>
       </c>
       <c r="I47" t="n">
         <v>2884.695282501625</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K47" t="n">
-        <v>5.35</v>
+        <v>3.4</v>
       </c>
       <c r="L47" t="n">
         <v>11.09</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45036</v>
+        <v>45037</v>
       </c>
       <c r="H48" t="n">
-        <v>3184.3</v>
+        <v>3153.3</v>
       </c>
       <c r="I48" t="n">
         <v>3174.45402676105</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K48" t="n">
-        <v>9.800000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="L48" t="n">
         <v>5.11</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>7.85</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45042</v>
+        <v>45043</v>
       </c>
       <c r="H49" t="n">
-        <v>3400.15</v>
+        <v>3411.6</v>
       </c>
       <c r="I49" t="n">
         <v>3400.98743329109</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K49" t="n">
-        <v>-7.83</v>
+        <v>-8.19</v>
       </c>
       <c r="L49" t="n">
-        <v>8.050000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="M49" t="n">
         <v>0.43</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.23</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45126</v>
+        <v>45127</v>
       </c>
       <c r="H50" t="n">
-        <v>4493.5</v>
+        <v>4204</v>
       </c>
       <c r="I50" t="n">
         <v>4239.450498194847</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K50" t="n">
-        <v>31.71</v>
+        <v>23.23</v>
       </c>
       <c r="L50" t="n">
         <v>1.04</v>
@@ -3291,7 +3890,7 @@
         <v>0.64</v>
       </c>
       <c r="N50" t="n">
-        <v>4.39</v>
+        <v>6.44</v>
       </c>
       <c r="O50" t="n">
         <v>0.34</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>12.1</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45177</v>
+        <v>45180</v>
       </c>
       <c r="H51" t="n">
-        <v>4458.55</v>
+        <v>4618.85</v>
       </c>
       <c r="I51" t="n">
         <v>4562.171937296351</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.05</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>9.609999999999999</v>
+        <v>11.27</v>
       </c>
       <c r="M51" t="n">
         <v>0.73</v>
       </c>
       <c r="N51" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="O51" t="n">
         <v>-6.44</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>7.9</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45190</v>
+        <v>45191</v>
       </c>
       <c r="H52" t="n">
-        <v>4276.2</v>
+        <v>4187</v>
       </c>
       <c r="I52" t="n">
         <v>4253.831917995878</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.42</v>
+        <v>-9.35</v>
       </c>
       <c r="L52" t="n">
-        <v>7.77</v>
+        <v>9.83</v>
       </c>
       <c r="M52" t="n">
         <v>0.42</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.56</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="H53" t="n">
-        <v>4208.8</v>
+        <v>4275.55</v>
       </c>
       <c r="I53" t="n">
         <v>4243.011087246409</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.52</v>
+        <v>-2.11</v>
       </c>
       <c r="L53" t="n">
         <v>3.64</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>7.16</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="H54" t="n">
-        <v>4671.6</v>
+        <v>4546.05</v>
       </c>
       <c r="I54" t="n">
         <v>4551.687870006334</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K54" t="n">
-        <v>9.26</v>
+        <v>6.33</v>
       </c>
       <c r="L54" t="n">
         <v>1.87</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>9.52</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45342</v>
+        <v>45343</v>
       </c>
       <c r="H55" t="n">
-        <v>4524.5</v>
+        <v>4984.7</v>
       </c>
       <c r="I55" t="n">
         <v>4830.979099642717</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>0.47</v>
+        <v>-9.65</v>
       </c>
       <c r="L55" t="n">
-        <v>3.34</v>
+        <v>12.93</v>
       </c>
       <c r="M55" t="n">
-        <v>0.93</v>
+        <v>2.55</v>
       </c>
       <c r="N55" t="n">
-        <v>3.91</v>
+        <v>10.17</v>
       </c>
       <c r="O55" t="n">
         <v>-2.69</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>12.76</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H56" t="n">
-        <v>8728</v>
+        <v>7666.75</v>
       </c>
       <c r="I56" t="n">
         <v>7888.194934539746</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K56" t="n">
-        <v>75.09999999999999</v>
+        <v>53.81</v>
       </c>
       <c r="L56" t="n">
         <v>6.92</v>
@@ -3633,7 +4304,7 @@
         <v>1.45</v>
       </c>
       <c r="N56" t="n">
-        <v>4.14</v>
+        <v>12.16</v>
       </c>
       <c r="O56" t="n">
         <v>10.17</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>17.64</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45456</v>
+        <v>45457</v>
       </c>
       <c r="H57" t="n">
-        <v>8446.6</v>
+        <v>9020</v>
       </c>
       <c r="I57" t="n">
         <v>8805.305353022804</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K57" t="n">
-        <v>-10.17</v>
+        <v>-17.65</v>
       </c>
       <c r="L57" t="n">
-        <v>14.13</v>
+        <v>19.28</v>
       </c>
       <c r="M57" t="n">
         <v>2.39</v>
       </c>
       <c r="N57" t="n">
-        <v>2.29</v>
+        <v>6.79</v>
       </c>
       <c r="O57" t="n">
         <v>-12.16</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>14.65</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45489</v>
+        <v>45491</v>
       </c>
       <c r="H58" t="n">
-        <v>8232.299999999999</v>
+        <v>7893.15</v>
       </c>
       <c r="I58" t="n">
         <v>7900.678465822757</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K58" t="n">
-        <v>-8.73</v>
+        <v>-12.49</v>
       </c>
       <c r="L58" t="n">
-        <v>10.04</v>
+        <v>14.49</v>
       </c>
       <c r="M58" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>3.64</v>
+        <v>4.12</v>
       </c>
       <c r="O58" t="n">
         <v>6.79</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>10.81</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45559</v>
+        <v>45560</v>
       </c>
       <c r="H59" t="n">
-        <v>8078.2</v>
+        <v>8178.35</v>
       </c>
       <c r="I59" t="n">
         <v>8101.949824370191</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.34</v>
+        <v>-3.61</v>
       </c>
       <c r="L59" t="n">
         <v>4.7</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45587</v>
+        <v>45588</v>
       </c>
       <c r="H60" t="n">
-        <v>8177.55</v>
+        <v>7703.8</v>
       </c>
       <c r="I60" t="n">
         <v>8039.969896772463</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.01</v>
+        <v>-5.8</v>
       </c>
       <c r="L60" t="n">
-        <v>6.19</v>
+        <v>6.82</v>
       </c>
       <c r="M60" t="n">
         <v>1.95</v>
       </c>
       <c r="N60" t="n">
-        <v>5.73</v>
+        <v>5.79</v>
       </c>
       <c r="O60" t="n">
         <v>1.24</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>15.14</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="H61" t="n">
-        <v>7329.7</v>
+        <v>7496.2</v>
       </c>
       <c r="I61" t="n">
         <v>7422.785188704062</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K61" t="n">
-        <v>4.86</v>
+        <v>2.69</v>
       </c>
       <c r="L61" t="n">
         <v>6.44</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>10.35</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H62" t="n">
-        <v>7351.9</v>
+        <v>6921.25</v>
       </c>
       <c r="I62" t="n">
         <v>7330.941644000856</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.92</v>
+        <v>-7.67</v>
       </c>
       <c r="L62" t="n">
-        <v>2.4</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M62" t="n">
         <v>0.58</v>
       </c>
       <c r="N62" t="n">
-        <v>3.99</v>
+        <v>5.86</v>
       </c>
       <c r="O62" t="n">
         <v>2.27</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>13.15</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="H63" t="n">
-        <v>5379.5</v>
+        <v>5571.5</v>
       </c>
       <c r="I63" t="n">
         <v>5463.878193598475</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K63" t="n">
-        <v>22.28</v>
+        <v>19.5</v>
       </c>
       <c r="L63" t="n">
         <v>7.02</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>5</v>
+      </c>
+      <c r="U63" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>12.66</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="H64" t="n">
-        <v>5893.5</v>
+        <v>5756.5</v>
       </c>
       <c r="I64" t="n">
         <v>5824.779426321948</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K64" t="n">
-        <v>5.78</v>
+        <v>3.32</v>
       </c>
       <c r="L64" t="n">
         <v>6.85</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.95</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="H65" t="n">
-        <v>5248.6</v>
+        <v>5338.8</v>
       </c>
       <c r="I65" t="n">
         <v>5299.1384433388</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K65" t="n">
-        <v>8.82</v>
+        <v>7.26</v>
       </c>
       <c r="L65" t="n">
         <v>2.44</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>5.76</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H66" t="n">
-        <v>5200.7</v>
+        <v>5173.4</v>
       </c>
       <c r="I66" t="n">
         <v>5186.193533739275</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.59</v>
+        <v>-3.1</v>
       </c>
       <c r="L66" t="n">
-        <v>2.9</v>
+        <v>4.08</v>
       </c>
       <c r="M66" t="n">
         <v>0.13</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,25 +5042,25 @@
         <v>5.11</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45987</v>
+        <v>45988</v>
       </c>
       <c r="H67" t="n">
-        <v>5197.5</v>
+        <v>5240.5</v>
       </c>
       <c r="I67" t="n">
         <v>5212.753509694949</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.47</v>
+        <v>-1.3</v>
       </c>
       <c r="L67" t="n">
         <v>3.28</v>
       </c>
       <c r="M67" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="N67" t="n">
         <v>2.5</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>5.51</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="H68" t="n">
-        <v>5048</v>
+        <v>4966</v>
       </c>
       <c r="I68" t="n">
         <v>4986.116012089133</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.67</v>
+        <v>-5.24</v>
       </c>
       <c r="L68" t="n">
-        <v>5.52</v>
+        <v>6.06</v>
       </c>
       <c r="M68" t="n">
         <v>0.39</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>8.32</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="H69" t="n">
-        <v>5043.5</v>
+        <v>5474</v>
       </c>
       <c r="I69" t="n">
         <v>5065.155101034698</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.56</v>
+        <v>-10.23</v>
       </c>
       <c r="L69" t="n">
-        <v>2.33</v>
+        <v>11.71</v>
       </c>
       <c r="M69" t="n">
         <v>1.09</v>
       </c>
       <c r="N69" t="n">
-        <v>7.14</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O69" t="n">
         <v>-1.62</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>14.06</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="H70" t="n">
-        <v>7012.5</v>
+        <v>6387.5</v>
       </c>
       <c r="I70" t="n">
         <v>6859.005355528398</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K70" t="n">
-        <v>28.11</v>
+        <v>16.69</v>
       </c>
       <c r="L70" t="n">
         <v>8.960000000000001</v>
       </c>
       <c r="M70" t="n">
-        <v>3.84</v>
+        <v>5</v>
       </c>
       <c r="N70" t="n">
-        <v>4.06</v>
+        <v>8.91</v>
       </c>
       <c r="O70" t="n">
         <v>8.539999999999999</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>14.62</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="H71" t="n">
-        <v>6804</v>
+        <v>7219</v>
       </c>
       <c r="I71" t="n">
         <v>7055.684064374616</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K71" t="n">
-        <v>-6.52</v>
+        <v>-13.02</v>
       </c>
       <c r="L71" t="n">
-        <v>6.86</v>
+        <v>13.41</v>
       </c>
       <c r="M71" t="n">
         <v>1.03</v>
       </c>
       <c r="N71" t="n">
-        <v>4.36</v>
+        <v>6.1</v>
       </c>
       <c r="O71" t="n">
         <v>-8.91</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>12.2</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H72" t="n">
-        <v>7274</v>
+        <v>7005</v>
       </c>
       <c r="I72" t="n">
         <v>7145.19526064145</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K72" t="n">
-        <v>0.76</v>
+        <v>-2.96</v>
       </c>
       <c r="L72" t="n">
         <v>7.84</v>
@@ -4545,7 +5408,7 @@
         <v>1.53</v>
       </c>
       <c r="N72" t="n">
-        <v>3.17</v>
+        <v>3.7</v>
       </c>
       <c r="O72" t="n">
         <v>6.1</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>4</v>
+      </c>
+      <c r="U72" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,14 @@
       <c r="Q73" t="n">
         <v>30</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9563,7 +10446,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -9573,7 +10456,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -9583,7 +10466,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8">
@@ -9593,7 +10476,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -9603,7 +10486,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83.5</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="10">
@@ -9613,7 +10496,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11">
@@ -9653,7 +10536,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.41</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="15">
@@ -9663,7 +10546,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.66</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="16">
@@ -9673,7 +10556,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.06</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="17">
@@ -9683,7 +10566,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>75.09999999999999</v>
+        <v>53.81</v>
       </c>
     </row>
     <row r="18">
@@ -9693,7 +10576,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.5</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="19">
@@ -9703,7 +10586,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.21</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="20">
@@ -9713,7 +10596,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.19</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="21">
@@ -9723,7 +10606,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.19</v>
+        <v>19.28</v>
       </c>
     </row>
     <row r="22">
@@ -9733,7 +10616,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -9743,7 +10626,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -9753,7 +10636,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="25">
@@ -9773,7 +10656,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.03</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="27">
@@ -9783,7 +10666,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.37</v>
+        <v>14.48</v>
       </c>
     </row>
     <row r="28">
@@ -9793,7 +10676,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
